--- a/OUT_EXCEL/out_9.xlsx
+++ b/OUT_EXCEL/out_9.xlsx
@@ -450,12 +450,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ham</t>
+          <t>Hàm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Chuc nang</t>
+          <t>Chúc nang</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tinh tong.</t>
+          <t>Tinh tong</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tinh trung binh</t>
+          <t>Tinh tung binh</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tim GTNN</t>
+          <t>TimGI</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tim GTLN</t>
+          <t>Tim GILN</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dem</t>
+          <t>Đếm</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dem (co dieu kien)</t>
+          <t>Đếm (co đicu kên</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>if</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dieu kien</t>
+          <t>Đlukien</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tinh tong (co dieu kien).</t>
+          <t>Innh tông (có điêu ken)</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>vlookup</t>
+          <t>Flookup</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tim gia tri theo hang</t>
+          <t>Tim giá tri theo hang</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tim gia tri theo cot</t>
+          <t>Tim giá tri theo cot</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>index +match</t>
+          <t>idex _match</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ket hop de tim gia tri theo ca hang va cot.</t>
+          <t>Kễhop đzm giátihheo c hangàcô</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Va (can thoa man 2 dieu kien).</t>
+          <t>Và(can thoa mãn 2 điu kien)</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hoac (thoa man 1 trong 2 dieu kien)</t>
+          <t>Hoăc (thoa măn ! trong 2 đicu kiên)</t>
         </is>
       </c>
     </row>
@@ -725,17 +725,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Lef</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lay n ky tu cua 1 doan text ti ben trai.</t>
+          <t>Lavnký t cua 1 đoan text tù bên tái</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Rght</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lay n ky tur cua 1 doan text tir ben phai</t>
+          <t>Lkt"cúa l đoan text @ubên phai</t>
         </is>
       </c>
     </row>
